--- a/raw_data/auction_com/Event_inventory_cb_E-32411I_2026-10-14.xlsx
+++ b/raw_data/auction_com/Event_inventory_cb_E-32411I_2026-10-14.xlsx
@@ -134,157 +134,157 @@
     <t>960.0</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>1998</t>
+  </si>
+  <si>
+    <t>9658-4748</t>
+  </si>
+  <si>
+    <t>576 WRIGHT ROAD</t>
+  </si>
+  <si>
+    <t>BANDERA</t>
+  </si>
+  <si>
+    <t>Bandera</t>
+  </si>
+  <si>
+    <t>78003</t>
+  </si>
+  <si>
+    <t>2128</t>
+  </si>
+  <si>
+    <t>TS 10933000</t>
+  </si>
+  <si>
+    <t>214 HENRIETTA DR</t>
+  </si>
+  <si>
+    <t>CENTER</t>
+  </si>
+  <si>
+    <t>Shelby</t>
+  </si>
+  <si>
+    <t>75935</t>
+  </si>
+  <si>
+    <t>1280.0</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>1985</t>
+  </si>
+  <si>
+    <t>TS 10956100</t>
+  </si>
+  <si>
+    <t>407 NORTH CONNETT STREET</t>
+  </si>
+  <si>
+    <t>LEONARD</t>
+  </si>
+  <si>
+    <t>Fannin</t>
+  </si>
+  <si>
+    <t>75452</t>
+  </si>
+  <si>
+    <t>1472</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>1935</t>
+  </si>
+  <si>
+    <t>TS 10950194</t>
+  </si>
+  <si>
+    <t>131 CLYDESDALE LN</t>
+  </si>
+  <si>
+    <t>VICTORIA</t>
+  </si>
+  <si>
+    <t>77904</t>
+  </si>
+  <si>
+    <t>1339</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>TS 10928539</t>
+  </si>
+  <si>
+    <t>5760 US HIGHWAY 67 WEST</t>
+  </si>
+  <si>
+    <t>OMAHA</t>
+  </si>
+  <si>
+    <t>Morris</t>
+  </si>
+  <si>
+    <t>75571</t>
+  </si>
+  <si>
+    <t>2280.0</t>
+  </si>
+  <si>
+    <t>1.23</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>TX-26-133466-POS</t>
+  </si>
+  <si>
+    <t>134 SYCAMORE ST.</t>
+  </si>
+  <si>
+    <t>ALTO</t>
+  </si>
+  <si>
+    <t>Cherokee</t>
+  </si>
+  <si>
+    <t>75925</t>
+  </si>
+  <si>
+    <t>1044</t>
+  </si>
+  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>2.0</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>1998</t>
-  </si>
-  <si>
-    <t>9658-4748</t>
-  </si>
-  <si>
-    <t>576 WRIGHT ROAD</t>
-  </si>
-  <si>
-    <t>BANDERA</t>
-  </si>
-  <si>
-    <t>Bandera</t>
-  </si>
-  <si>
-    <t>78003</t>
-  </si>
-  <si>
-    <t>2128</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>TS 10933000</t>
-  </si>
-  <si>
-    <t>214 HENRIETTA DR</t>
-  </si>
-  <si>
-    <t>CENTER</t>
-  </si>
-  <si>
-    <t>Shelby</t>
-  </si>
-  <si>
-    <t>75935</t>
-  </si>
-  <si>
-    <t>1280.0</t>
-  </si>
-  <si>
-    <t>0.58</t>
-  </si>
-  <si>
-    <t>1985</t>
-  </si>
-  <si>
-    <t>TS 10956100</t>
-  </si>
-  <si>
-    <t>407 NORTH CONNETT STREET</t>
-  </si>
-  <si>
-    <t>LEONARD</t>
-  </si>
-  <si>
-    <t>Fannin</t>
-  </si>
-  <si>
-    <t>75452</t>
-  </si>
-  <si>
-    <t>1472</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>2.5</t>
-  </si>
-  <si>
-    <t>0.43</t>
-  </si>
-  <si>
-    <t>1935</t>
-  </si>
-  <si>
-    <t>TS 10950194</t>
-  </si>
-  <si>
-    <t>131 CLYDESDALE LN</t>
-  </si>
-  <si>
-    <t>VICTORIA</t>
-  </si>
-  <si>
-    <t>77904</t>
-  </si>
-  <si>
-    <t>1339</t>
-  </si>
-  <si>
-    <t>0.21</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>TS 10928539</t>
-  </si>
-  <si>
-    <t>5760 US HIGHWAY 67 WEST</t>
-  </si>
-  <si>
-    <t>OMAHA</t>
-  </si>
-  <si>
-    <t>Morris</t>
-  </si>
-  <si>
-    <t>75571</t>
-  </si>
-  <si>
-    <t>2280.0</t>
-  </si>
-  <si>
-    <t>1.23</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>TX-26-133466-POS</t>
-  </si>
-  <si>
-    <t>134 SYCAMORE ST.</t>
-  </si>
-  <si>
-    <t>ALTO</t>
-  </si>
-  <si>
-    <t>Cherokee</t>
-  </si>
-  <si>
-    <t>75925</t>
-  </si>
-  <si>
-    <t>1044</t>
   </si>
   <si>
     <t>0.51</t>
@@ -2565,16 +2565,16 @@
         <v>49</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s" s="2">
         <v>42</v>
       </c>
       <c r="N4" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O4" t="n" s="3">
         <v>196668.0</v>
@@ -2587,7 +2587,7 @@
         <v>33</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -2595,43 +2595,43 @@
         <v>19</v>
       </c>
       <c r="B5" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="D5" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="C5" t="s" s="2">
+      <c r="E5" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D5" t="s" s="2">
+      <c r="G5" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="I5" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="J5" t="s" s="2">
         <v>55</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F5" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="G5" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="H5" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="J5" t="s" s="2">
-        <v>57</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>29</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O5" t="s" s="2">
         <v>33</v>
@@ -2644,7 +2644,7 @@
         <v>33</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
@@ -2652,43 +2652,43 @@
         <v>19</v>
       </c>
       <c r="B6" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="D6" t="s" s="2">
         <v>61</v>
       </c>
-      <c r="C6" t="s" s="2">
+      <c r="E6" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="D6" t="s" s="2">
+      <c r="G6" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="J6" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="E6" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F6" t="s" s="2">
+      <c r="K6" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="G6" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="H6" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="I6" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="J6" t="s" s="2">
+      <c r="L6" t="s" s="2">
         <v>65</v>
       </c>
-      <c r="K6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>67</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="O6" t="n" s="3">
         <v>258947.0</v>
@@ -2701,7 +2701,7 @@
         <v>33</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -2709,43 +2709,43 @@
         <v>19</v>
       </c>
       <c r="B7" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="C7" t="s" s="2">
+      <c r="G7" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="J7" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
         <v>29</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="O7" t="n" s="3">
         <v>234316.0</v>
@@ -2758,7 +2758,7 @@
         <v>33</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -2766,43 +2766,43 @@
         <v>19</v>
       </c>
       <c r="B8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="C8" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="C8" t="s" s="2">
+      <c r="D8" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="D8" t="s" s="2">
+      <c r="E8" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F8" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="E8" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F8" t="s" s="2">
+      <c r="G8" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="J8" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="G8" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K8" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L8" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>83</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="O8" t="s" s="2">
         <v>33</v>
@@ -2815,7 +2815,7 @@
         <v>33</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -2823,34 +2823,34 @@
         <v>19</v>
       </c>
       <c r="B9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="C9" t="s" s="2">
+      <c r="D9" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="D9" t="s" s="2">
+      <c r="E9" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="E9" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F9" t="s" s="2">
+      <c r="G9" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="J9" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G9" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="I9" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="J9" t="s" s="2">
+      <c r="K9" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="K9" t="s" s="2">
-        <v>40</v>
       </c>
       <c r="L9" t="s" s="2">
         <v>30</v>
@@ -2910,7 +2910,7 @@
         <v>29</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M10" t="s" s="2">
         <v>100</v>
@@ -3021,7 +3021,7 @@
         <v>115</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>116</v>
@@ -3078,10 +3078,10 @@
         <v>124</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M13" t="s" s="2">
         <v>125</v>
@@ -3135,10 +3135,10 @@
         <v>132</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M14" t="s" s="2">
         <v>133</v>
@@ -3249,10 +3249,10 @@
         <v>148</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M16" t="s" s="2">
         <v>149</v>
@@ -3303,13 +3303,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K17" t="s" s="2">
         <v>29</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M17" t="s" s="2">
         <v>156</v>
@@ -3366,7 +3366,7 @@
         <v>29</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M18" t="s" s="2">
         <v>164</v>
@@ -3477,10 +3477,10 @@
         <v>178</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M20" t="s" s="2">
         <v>179</v>
@@ -3534,10 +3534,10 @@
         <v>186</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M21" t="s" s="2">
         <v>187</v>
@@ -3591,10 +3591,10 @@
         <v>194</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M22" t="s" s="2">
         <v>195</v>
@@ -3627,7 +3627,7 @@
         <v>200</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s" s="2">
         <v>23</v>
@@ -3708,7 +3708,7 @@
         <v>31</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M24" t="s" s="2">
         <v>213</v>
@@ -3762,16 +3762,16 @@
         <v>220</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>221</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O25" t="s" s="2">
         <v>33</v>
@@ -3876,7 +3876,7 @@
         <v>233</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>234</v>
@@ -3912,7 +3912,7 @@
         <v>239</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E28" t="s" s="2">
         <v>23</v>
@@ -3933,10 +3933,10 @@
         <v>33</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M28" t="s" s="2">
         <v>33</v>
@@ -3993,7 +3993,7 @@
         <v>29</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M29" t="s" s="2">
         <v>248</v>
@@ -4026,7 +4026,7 @@
         <v>252</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E30" t="s" s="2">
         <v>23</v>
@@ -4050,7 +4050,7 @@
         <v>29</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M30" t="s" s="2">
         <v>255</v>
@@ -4104,7 +4104,7 @@
         <v>262</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>30</v>
@@ -4161,10 +4161,10 @@
         <v>270</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M32" t="s" s="2">
         <v>229</v>
@@ -4218,10 +4218,10 @@
         <v>33</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M33" t="s" s="2">
         <v>33</v>
@@ -4278,7 +4278,7 @@
         <v>29</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M34" t="s" s="2">
         <v>279</v>
@@ -4335,13 +4335,13 @@
         <v>29</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M35" t="s" s="2">
         <v>42</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O35" t="n" s="3">
         <v>515489.0</v>
@@ -4389,7 +4389,7 @@
         <v>291</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>292</v>
@@ -4422,16 +4422,16 @@
         <v>297</v>
       </c>
       <c r="C37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D37" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="D37" t="s" s="2">
+      <c r="E37" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F37" t="s" s="2">
         <v>80</v>
-      </c>
-      <c r="E37" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F37" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>25</v>
@@ -4446,7 +4446,7 @@
         <v>298</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>30</v>
@@ -4455,7 +4455,7 @@
         <v>299</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O37" t="s" s="2">
         <v>33</v>
@@ -4506,7 +4506,7 @@
         <v>29</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M38" t="s" s="2">
         <v>304</v>
@@ -4563,7 +4563,7 @@
         <v>29</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M39" t="s" s="2">
         <v>100</v>
@@ -4620,7 +4620,7 @@
         <v>29</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M40" t="s" s="2">
         <v>316</v>
@@ -4674,10 +4674,10 @@
         <v>323</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M41" t="s" s="2">
         <v>324</v>
@@ -4731,7 +4731,7 @@
         <v>329</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>30</v>
@@ -4788,16 +4788,16 @@
         <v>336</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>234</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O43" t="n" s="3">
         <v>144642.0</v>
@@ -4881,7 +4881,7 @@
         <v>252</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E45" t="s" s="2">
         <v>23</v>
@@ -4905,7 +4905,7 @@
         <v>29</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M45" t="s" s="2">
         <v>348</v>
@@ -4959,10 +4959,10 @@
         <v>354</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M46" t="s" s="2">
         <v>221</v>
@@ -5016,16 +5016,16 @@
         <v>362</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M47" t="s" s="2">
         <v>363</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O47" t="s" s="2">
         <v>33</v>
@@ -5073,7 +5073,7 @@
         <v>228</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>234</v>
@@ -5109,7 +5109,7 @@
         <v>372</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E49" t="s" s="2">
         <v>23</v>
@@ -5130,7 +5130,7 @@
         <v>374</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>292</v>
@@ -5244,7 +5244,7 @@
         <v>387</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>292</v>
@@ -5301,10 +5301,10 @@
         <v>394</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M52" t="s" s="2">
         <v>395</v>
@@ -5358,16 +5358,16 @@
         <v>402</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M53" t="s" s="2">
         <v>403</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O53" t="n" s="3">
         <v>162283.0</v>
@@ -5415,10 +5415,10 @@
         <v>410</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M54" t="s" s="2">
         <v>411</v>
@@ -5532,7 +5532,7 @@
         <v>29</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M56" t="s" s="2">
         <v>133</v>
@@ -5589,7 +5589,7 @@
         <v>29</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M57" t="s" s="2">
         <v>395</v>
@@ -5643,7 +5643,7 @@
         <v>439</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>30</v>
@@ -5697,10 +5697,10 @@
         <v>27</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>30</v>
@@ -5757,7 +5757,7 @@
         <v>450</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>292</v>
@@ -5814,16 +5814,16 @@
         <v>458</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M61" t="s" s="2">
         <v>459</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O61" t="n" s="3">
         <v>204563.0</v>
@@ -5871,16 +5871,16 @@
         <v>465</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M62" t="s" s="2">
         <v>466</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>33</v>
@@ -5925,13 +5925,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K63" t="s" s="2">
         <v>29</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M63" t="s" s="2">
         <v>420</v>
@@ -6042,7 +6042,7 @@
         <v>486</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>30</v>
@@ -6099,7 +6099,7 @@
         <v>493</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>30</v>
@@ -6159,13 +6159,13 @@
         <v>29</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M67" t="s" s="2">
         <v>420</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O67" t="n" s="3">
         <v>207817.0</v>
@@ -6213,10 +6213,10 @@
         <v>504</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M68" t="s" s="2">
         <v>221</v>
@@ -6267,19 +6267,19 @@
         <v>511</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M69" t="s" s="2">
         <v>512</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O69" t="s" s="2">
         <v>33</v>
@@ -6327,16 +6327,16 @@
         <v>325</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M70" t="s" s="2">
         <v>304</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O70" t="n" s="3">
         <v>251765.0</v>
@@ -6384,10 +6384,10 @@
         <v>33</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M71" t="s" s="2">
         <v>33</v>
@@ -6441,7 +6441,7 @@
         <v>524</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>30</v>
@@ -6501,7 +6501,7 @@
         <v>29</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M73" t="s" s="2">
         <v>533</v>
@@ -6555,7 +6555,7 @@
         <v>539</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L74" t="s" s="2">
         <v>234</v>
@@ -6615,10 +6615,10 @@
         <v>29</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>384</v>
@@ -6669,10 +6669,10 @@
         <v>194</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M76" t="s" s="2">
         <v>551</v>
@@ -6783,10 +6783,10 @@
         <v>33</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M78" t="s" s="2">
         <v>33</v>
@@ -6840,13 +6840,13 @@
         <v>563</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>126</v>
@@ -6897,16 +6897,16 @@
         <v>569</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M80" t="s" s="2">
         <v>570</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O80" t="s" s="2">
         <v>33</v>
@@ -6951,13 +6951,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M81" t="s" s="2">
         <v>575</v>
@@ -7011,10 +7011,10 @@
         <v>579</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M82" t="s" s="2">
         <v>316</v>
@@ -7065,19 +7065,19 @@
         <v>511</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M83" t="s" s="2">
         <v>584</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O83" t="s" s="2">
         <v>33</v>
@@ -7125,7 +7125,7 @@
         <v>589</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L84" t="s" s="2">
         <v>30</v>
@@ -7185,7 +7185,7 @@
         <v>29</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M85" t="s" s="2">
         <v>213</v>
@@ -7296,7 +7296,7 @@
         <v>607</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L87" t="s" s="2">
         <v>292</v>
@@ -7353,10 +7353,10 @@
         <v>612</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M88" t="s" s="2">
         <v>395</v>
@@ -7410,10 +7410,10 @@
         <v>33</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M89" t="s" s="2">
         <v>33</v>
@@ -7470,13 +7470,13 @@
         <v>29</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M90" t="s" s="2">
         <v>624</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>33</v>
@@ -7500,7 +7500,7 @@
         <v>627</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>628</v>
@@ -7509,7 +7509,7 @@
         <v>23</v>
       </c>
       <c r="F91" t="s" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>114</v>
@@ -7521,10 +7521,10 @@
         <v>381</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="L91" t="s" s="2">
         <v>30</v>
@@ -7581,10 +7581,10 @@
         <v>637</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M92" t="s" s="2">
         <v>213</v>
@@ -7638,7 +7638,7 @@
         <v>644</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L93" t="s" s="2">
         <v>30</v>
@@ -7695,7 +7695,7 @@
         <v>648</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L94" t="s" s="2">
         <v>30</v>
@@ -7752,7 +7752,7 @@
         <v>653</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L95" t="s" s="2">
         <v>30</v>
@@ -7809,10 +7809,10 @@
         <v>660</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M96" t="s" s="2">
         <v>661</v>
@@ -7845,7 +7845,7 @@
         <v>666</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E97" t="s" s="2">
         <v>23</v>
@@ -7869,7 +7869,7 @@
         <v>29</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M97" t="s" s="2">
         <v>304</v>
@@ -7923,16 +7923,16 @@
         <v>673</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M98" t="s" s="2">
         <v>674</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O98" t="s" s="2">
         <v>33</v>
@@ -7980,13 +7980,13 @@
         <v>680</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>662</v>
@@ -8040,7 +8040,7 @@
         <v>29</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M100" t="s" s="2">
         <v>117</v>
@@ -8091,19 +8091,19 @@
         <v>511</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M101" t="s" s="2">
         <v>304</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O101" t="s" s="2">
         <v>33</v>
@@ -8154,7 +8154,7 @@
         <v>29</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M102" t="s" s="2">
         <v>440</v>
@@ -8211,7 +8211,7 @@
         <v>29</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M103" t="s" s="2">
         <v>700</v>
@@ -8268,7 +8268,7 @@
         <v>29</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M104" t="s" s="2">
         <v>420</v>
@@ -8385,7 +8385,7 @@
         <v>30</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>110</v>
@@ -8436,10 +8436,10 @@
         <v>722</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M107" t="s" s="2">
         <v>459</v>
@@ -8493,10 +8493,10 @@
         <v>728</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M108" t="s" s="2">
         <v>729</v>
@@ -8550,10 +8550,10 @@
         <v>33</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M109" t="s" s="2">
         <v>33</v>
@@ -8607,16 +8607,16 @@
         <v>739</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="M110" t="s" s="2">
         <v>420</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O110" t="n" s="3">
         <v>243562.0</v>
@@ -8667,7 +8667,7 @@
         <v>29</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="M111" t="s" s="2">
         <v>248</v>
